--- a/Data/Fertilizacion.xlsx
+++ b/Data/Fertilizacion.xlsx
@@ -1,24 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/a_f_velez_cgiar_org/Documents/R_projects/Fertilice_right/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{C28896A2-796A-4CB0-82A9-E961783AB2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FFCE800-31BF-48E5-AB0C-01AD1812F2C0}"/>
+  <xr:revisionPtr revIDLastSave="447" documentId="8_{C28896A2-796A-4CB0-82A9-E961783AB2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07216216-D9E3-4A39-AEEC-927288019547}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="1035" windowWidth="24240" windowHeight="13020" xr2:uid="{10C628A5-A26D-4D12-8800-9B5424EF2003}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{10C628A5-A26D-4D12-8800-9B5424EF2003}"/>
   </bookViews>
   <sheets>
     <sheet name="Fertilizations" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fertilizations!$A$1:$J$149</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
+  <pivotCaches>
+    <pivotCache cacheId="15" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="71">
   <si>
     <t>Finca</t>
   </si>
@@ -241,6 +245,18 @@
   <si>
     <t>Aporte NO3 (kg/ha)</t>
   </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Average of Cantidad_Kg_ha</t>
+  </si>
 </sst>
 </file>
 
@@ -281,9 +297,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -299,6 +320,4236 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Fertilizacion.xlsx]Sheet3!PivotTable2</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$B$5:$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Fertilizacion 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$7:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$B$7:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>112.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D835-4153-BCE6-77F6649040E4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$C$5:$C$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Fertilizacion 2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$7:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$C$7:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="1">
+                  <c:v>64.099999999999994</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-D835-4153-BCE6-77F6649040E4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$D$5:$D$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Fertilizacion 3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$7:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$D$7:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="2">
+                  <c:v>58.333333333333336</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-D835-4153-BCE6-77F6649040E4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$E$5:$E$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Fertilizacion 4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$7:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$E$7:$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="3">
+                  <c:v>50.150000000000006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-D835-4153-BCE6-77F6649040E4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$F$5:$F$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Fertilizacion 5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$7:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$F$7:$F$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="4">
+                  <c:v>58.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-D835-4153-BCE6-77F6649040E4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="34925" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="90000"/>
+                  <a:alpha val="33000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="810228688"/>
+        <c:axId val="810228208"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="810228688"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="810228208"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="810228208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="810228688"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:blipFill dpi="0" rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect t="39000" r="-37000" b="-29000"/>
+          </a:stretch>
+        </a:blipFill>
+        <a:ln w="41275">
+          <a:noFill/>
+          <a:prstDash val="lgDashDot"/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="230">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="0" kern="1200" spc="20" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+            <a:alpha val="33000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="95000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" spc="20" baseline="0"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>104773</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>66674</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7A5C035-9F5F-BF8C-24B8-2703993F1E01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="afvelez" refreshedDate="45755.616168865738" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="148" xr:uid="{9829125B-7E6E-4173-AF6B-525EC64E6B80}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:M149" sheet="Fertilizations"/>
+  </cacheSource>
+  <cacheFields count="13">
+    <cacheField name="Finca" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Farm_1"/>
+        <s v="Farm_2"/>
+        <s v="Farm_3"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="DDS" numFmtId="0">
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="59" maxValue="59" count="24">
+        <s v="25"/>
+        <s v="26"/>
+        <s v="33"/>
+        <s v="45"/>
+        <s v="43"/>
+        <s v="59"/>
+        <s v="62"/>
+        <s v="80"/>
+        <s v="79"/>
+        <s v="24"/>
+        <s v="39"/>
+        <s v="49"/>
+        <s v="74"/>
+        <n v="59"/>
+        <s v="163"/>
+        <s v="197"/>
+        <s v="215"/>
+        <s v="263"/>
+        <s v="168"/>
+        <s v="161"/>
+        <s v="221"/>
+        <s v="270"/>
+        <s v="160"/>
+        <s v="183"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Cultivo" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Arroz"/>
+        <s v="Banano"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Activity" numFmtId="0">
+      <sharedItems count="5">
+        <s v="Fertilizacion 1"/>
+        <s v="Fertilizacion 2"/>
+        <s v="Fertilizacion 3"/>
+        <s v="Fertilizacion 4"/>
+        <s v="Fertilizacion 5"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Tratamiento" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Convencional"/>
+        <s v="Optimizado"/>
+        <s v="Alternativo"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Cantidad_Kg_ha" numFmtId="0">
+      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="0" maxValue="238"/>
+    </cacheField>
+    <cacheField name="Cantidad_L_ha" numFmtId="0">
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
+    </cacheField>
+    <cacheField name="Aporte N (Kg/ha)" numFmtId="0">
+      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="0" maxValue="54.2"/>
+    </cacheField>
+    <cacheField name="Aporte NH4 (kg/ha)" numFmtId="0">
+      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="0" maxValue="14.11"/>
+    </cacheField>
+    <cacheField name="Aporte NO3 (kg/ha)" numFmtId="0">
+      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="0" maxValue="54.2"/>
+    </cacheField>
+    <cacheField name="Aporte P (Kg/ha)" numFmtId="0">
+      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="0" maxValue="40"/>
+    </cacheField>
+    <cacheField name="Aporte K (Kg/ha)" numFmtId="0">
+      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="0" maxValue="64.260000000000005"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="148">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Triple 18"/>
+    <n v="200"/>
+    <s v="null"/>
+    <n v="36"/>
+    <n v="14"/>
+    <n v="22"/>
+    <n v="36"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Sulfazinc"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5.5"/>
+    <n v="9"/>
+    <n v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Triple 18"/>
+    <n v="55.5"/>
+    <s v="null"/>
+    <n v="9.99"/>
+    <n v="3.88"/>
+    <n v="6.1"/>
+    <n v="9.99"/>
+    <n v="9.99"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Triple 18"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="9"/>
+    <n v="3.5"/>
+    <n v="0"/>
+    <n v="0.75"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Sulfazinc"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1.5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Urea"/>
+    <n v="78.2"/>
+    <s v="null"/>
+    <n v="35.97"/>
+    <n v="0"/>
+    <n v="35.97"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Urea"/>
+    <n v="75"/>
+    <s v="null"/>
+    <n v="34.5"/>
+    <n v="0"/>
+    <n v="34.5"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="KCL"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="27"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="SAM"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="10.5"/>
+    <n v="10.5"/>
+    <n v="26.96"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Urea"/>
+    <n v="56.5"/>
+    <s v="null"/>
+    <n v="25.99"/>
+    <n v="0"/>
+    <n v="25.99"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Urea"/>
+    <n v="97.8"/>
+    <s v="null"/>
+    <n v="44.99"/>
+    <n v="0"/>
+    <n v="44.99"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Urea"/>
+    <n v="86.4"/>
+    <s v="null"/>
+    <n v="39.74"/>
+    <n v="0"/>
+    <n v="39.74"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="Urea"/>
+    <n v="58.7"/>
+    <s v="null"/>
+    <n v="27"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="30"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="KCL"/>
+    <n v="41.6"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="24.96"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="KCL"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="30"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Kieserita"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0.5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="0"/>
+    <s v="Urea"/>
+    <n v="58.6"/>
+    <s v="null"/>
+    <n v="26.96"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="SAM"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="5.25"/>
+    <n v="5.25"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="KCL"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="30"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="Urea"/>
+    <n v="117.3"/>
+    <s v="null"/>
+    <n v="53.96"/>
+    <n v="0"/>
+    <n v="53.96"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="KCL"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="30"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Triple 18"/>
+    <n v="200"/>
+    <s v="null"/>
+    <n v="36"/>
+    <n v="14"/>
+    <n v="22"/>
+    <n v="36"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Sulfazinc"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1.5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Triple 18"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="9"/>
+    <n v="3.5"/>
+    <n v="5.5"/>
+    <n v="9"/>
+    <n v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Urea"/>
+    <n v="75"/>
+    <s v="null"/>
+    <n v="34.5"/>
+    <n v="0"/>
+    <n v="34.5"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Kieserita"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Urea"/>
+    <n v="97.8"/>
+    <s v="null"/>
+    <n v="44.99"/>
+    <n v="0"/>
+    <n v="44.99"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="KCL"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="30"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Kieserita"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="Urea"/>
+    <n v="58.6"/>
+    <s v="null"/>
+    <n v="26.96"/>
+    <n v="0"/>
+    <n v="26.96"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="KCL"/>
+    <n v="41.6"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="24.96"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="12"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="0"/>
+    <s v="Urea"/>
+    <n v="39.1"/>
+    <s v="null"/>
+    <n v="17.989999999999998"/>
+    <n v="0"/>
+    <n v="17.989999999999998"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="57.5"/>
+    <s v="null"/>
+    <n v="23"/>
+    <n v="0"/>
+    <n v="23"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Sulfazinc"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0.75"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Microessentials"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="6"/>
+    <n v="6"/>
+    <n v="0"/>
+    <n v="20"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="0"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="100"/>
+    <s v="null"/>
+    <n v="40"/>
+    <n v="0"/>
+    <n v="40"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="80"/>
+    <s v="null"/>
+    <n v="32"/>
+    <n v="0"/>
+    <n v="32"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="1"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="60"/>
+    <s v="null"/>
+    <n v="24"/>
+    <n v="0"/>
+    <n v="24"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="79"/>
+    <s v="null"/>
+    <n v="31.6"/>
+    <n v="0"/>
+    <n v="31.6"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Sulfazinc"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1.5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Kornkali"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="96.2"/>
+    <s v="null"/>
+    <n v="38.479999999999997"/>
+    <n v="0"/>
+    <n v="38.479999999999997"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Kieserita"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0.5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Kornkali"/>
+    <n v="40"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="109.3"/>
+    <s v="null"/>
+    <n v="43.72"/>
+    <n v="0"/>
+    <n v="43.72"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Kornkali"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="135.5"/>
+    <s v="null"/>
+    <n v="54.2"/>
+    <n v="0"/>
+    <n v="54.2"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Kornkali"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="79"/>
+    <s v="null"/>
+    <n v="31.6"/>
+    <n v="0"/>
+    <n v="31.6"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Microessentials"/>
+    <n v="100"/>
+    <s v="null"/>
+    <n v="12"/>
+    <n v="12"/>
+    <n v="0"/>
+    <n v="40"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Sulfazinc"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1.5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="115"/>
+    <s v="null"/>
+    <n v="46"/>
+    <n v="0"/>
+    <n v="46"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Kieserita"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="106.2"/>
+    <s v="null"/>
+    <n v="42.48"/>
+    <n v="0"/>
+    <n v="42.48"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Kieserita"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="13"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="60"/>
+    <s v="null"/>
+    <n v="24"/>
+    <n v="0"/>
+    <n v="24"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="12"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="1"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="63.7"/>
+    <s v="null"/>
+    <n v="25.48"/>
+    <n v="0"/>
+    <n v="25.48"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="42"/>
+    <s v="null"/>
+    <n v="16.8"/>
+    <n v="0"/>
+    <n v="16.8"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Microessentials"/>
+    <n v="80"/>
+    <s v="null"/>
+    <n v="9.6"/>
+    <n v="9.6"/>
+    <n v="0"/>
+    <n v="32"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Sulfazinc"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1.5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Volcano"/>
+    <n v="75"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Fosfobiol"/>
+    <s v="null"/>
+    <n v="1"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Dimazos"/>
+    <s v="null"/>
+    <n v="1"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="103"/>
+    <s v="null"/>
+    <n v="41.2"/>
+    <n v="0"/>
+    <n v="41.2"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Kieserita"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Volcano"/>
+    <n v="75"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="95.6"/>
+    <s v="null"/>
+    <n v="38.24"/>
+    <n v="0"/>
+    <n v="38.24"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Kieserita"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="54"/>
+    <s v="null"/>
+    <n v="21.6"/>
+    <n v="0"/>
+    <n v="21.6"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="53"/>
+    <s v="null"/>
+    <n v="21.2"/>
+    <n v="0"/>
+    <n v="21.2"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Sulfazinc"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0.75"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Microessentials"/>
+    <n v="40"/>
+    <s v="null"/>
+    <n v="4.8"/>
+    <n v="4.8"/>
+    <n v="0"/>
+    <n v="16"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Volcano"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Fosfobiol"/>
+    <s v="null"/>
+    <n v="1"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Dimazos"/>
+    <s v="null"/>
+    <n v="1"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="79.2"/>
+    <s v="null"/>
+    <n v="31.68"/>
+    <n v="0"/>
+    <n v="31.68"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Volcano"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="90"/>
+    <s v="null"/>
+    <n v="36"/>
+    <n v="0"/>
+    <n v="36"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="72"/>
+    <s v="null"/>
+    <n v="28.8"/>
+    <n v="0"/>
+    <n v="28.8"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Kornkali"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="2"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="54"/>
+    <s v="null"/>
+    <n v="21.6"/>
+    <n v="0"/>
+    <n v="21.6"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="72.5"/>
+    <s v="null"/>
+    <n v="29"/>
+    <n v="0"/>
+    <n v="29"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Sulfazinc"/>
+    <n v="50"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1.5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Kornkali"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Volcano"/>
+    <n v="75"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Fosfobiol"/>
+    <s v="null"/>
+    <n v="1"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Dimazos"/>
+    <s v="null"/>
+    <n v="1"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+    <s v="null"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="88"/>
+    <s v="null"/>
+    <n v="35.200000000000003"/>
+    <n v="0"/>
+    <n v="35.200000000000003"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Kornkali"/>
+    <n v="40"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Kieserita"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0.5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Volcano"/>
+    <n v="75"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="100"/>
+    <s v="null"/>
+    <n v="40"/>
+    <n v="0"/>
+    <n v="40"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Kornkali"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Volcano"/>
+    <n v="75"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Nitroxtend XP-S"/>
+    <n v="129.5"/>
+    <s v="null"/>
+    <n v="51.8"/>
+    <n v="0"/>
+    <n v="51.8"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Kornkali"/>
+    <n v="25"/>
+    <s v="null"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="EMBAJADOR"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="40.799999999999997"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="6.12"/>
+    <n v="36.72"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Mezcla fisica YARA"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="24.48"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="8.16"/>
+    <n v="55.08"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Mezcla fisica YARA"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="24.48"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="8.16"/>
+    <n v="55.08"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="EMBAJADOR"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="40.799999999999997"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="6.12"/>
+    <n v="36.72"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="EMBAJADOR"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="40.799999999999997"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="6.12"/>
+    <n v="36.72"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Mezcla fisica YARA"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="24.48"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="8.16"/>
+    <n v="55.08"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Mezcla fisica YARA"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="24.48"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="8.16"/>
+    <n v="55.08"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="EMBAJADOR"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="40.799999999999997"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="6.12"/>
+    <n v="36.72"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="19"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="EMBAJADOR"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="40.799999999999997"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="6.12"/>
+    <n v="36.72"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="15"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Mezcla fisica YARA"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="24.48"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="8.16"/>
+    <n v="55.08"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="20"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Mezcla fisica YARA"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="24.48"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="8.16"/>
+    <n v="55.08"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="21"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="EMBAJADOR"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="40.799999999999997"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="6.12"/>
+    <n v="36.72"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Mezcla fisica 1"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="40.799999999999997"/>
+    <n v="2.04"/>
+    <n v="22.44"/>
+    <n v="6.12"/>
+    <n v="36.72"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Mezcla fisica 2"/>
+    <n v="170"/>
+    <s v="null"/>
+    <n v="20.399999999999999"/>
+    <n v="1.7"/>
+    <n v="18.7"/>
+    <n v="6.8"/>
+    <n v="45.9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Mezcla fisica 2"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="24.48"/>
+    <n v="2.04"/>
+    <n v="22.44"/>
+    <n v="8.16"/>
+    <n v="55.08"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Mezcla fisica 3"/>
+    <n v="136"/>
+    <s v="null"/>
+    <n v="27.2"/>
+    <n v="11.29"/>
+    <n v="9.11"/>
+    <n v="4.08"/>
+    <n v="24.48"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Mezcla fisica 1"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="40.799999999999997"/>
+    <n v="2.04"/>
+    <n v="22.44"/>
+    <n v="6.12"/>
+    <n v="36.72"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Mezcla fisica 2"/>
+    <n v="170"/>
+    <s v="null"/>
+    <n v="20.399999999999999"/>
+    <n v="1.7"/>
+    <n v="18.7"/>
+    <n v="6.8"/>
+    <n v="45.9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Mezcla fisica 2"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="24.48"/>
+    <n v="2.04"/>
+    <n v="22.44"/>
+    <n v="8.16"/>
+    <n v="55.08"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Mezcla fisica 3"/>
+    <n v="136"/>
+    <s v="null"/>
+    <n v="27.2"/>
+    <n v="11.29"/>
+    <n v="9.11"/>
+    <n v="4.08"/>
+    <n v="24.48"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="22"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Mezcla fisica 1"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="40.799999999999997"/>
+    <n v="2.04"/>
+    <n v="22.44"/>
+    <n v="6.12"/>
+    <n v="36.72"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Mezcla fisica 2"/>
+    <n v="170"/>
+    <s v="null"/>
+    <n v="20.399999999999999"/>
+    <n v="1.7"/>
+    <n v="18.7"/>
+    <n v="6.8"/>
+    <n v="45.9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="20"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Mezcla fisica 2"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="24.48"/>
+    <n v="2.04"/>
+    <n v="22.44"/>
+    <n v="8.16"/>
+    <n v="55.08"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="21"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Mezcla fisica 3"/>
+    <n v="136"/>
+    <s v="null"/>
+    <n v="27.2"/>
+    <n v="11.29"/>
+    <n v="9.11"/>
+    <n v="4.08"/>
+    <n v="24.48"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Mezcla fisica 1"/>
+    <n v="238"/>
+    <s v="null"/>
+    <n v="47.6"/>
+    <n v="2.38"/>
+    <n v="26.18"/>
+    <n v="7.14"/>
+    <n v="42.84"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Mezcla fisica 2"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="24.48"/>
+    <n v="2.04"/>
+    <n v="22.44"/>
+    <n v="8.16"/>
+    <n v="55.08"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Mezcla fisica 2"/>
+    <n v="238"/>
+    <s v="null"/>
+    <n v="28.56"/>
+    <n v="2.38"/>
+    <n v="26.18"/>
+    <n v="9.52"/>
+    <n v="64.260000000000005"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Mezcla fisica 3"/>
+    <n v="170"/>
+    <s v="null"/>
+    <n v="34"/>
+    <n v="14.11"/>
+    <n v="11.39"/>
+    <n v="5.0999999999999996"/>
+    <n v="30.6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Mezcla fisica 1"/>
+    <n v="238"/>
+    <s v="null"/>
+    <n v="47.6"/>
+    <n v="2.38"/>
+    <n v="26.18"/>
+    <n v="7.14"/>
+    <n v="42.84"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Mezcla fisica 2"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="24.48"/>
+    <n v="2.04"/>
+    <n v="22.44"/>
+    <n v="8.16"/>
+    <n v="55.08"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Mezcla fisica 2"/>
+    <n v="238"/>
+    <s v="null"/>
+    <n v="28.56"/>
+    <n v="2.38"/>
+    <n v="26.18"/>
+    <n v="9.52"/>
+    <n v="64.260000000000005"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Mezcla fisica 3"/>
+    <n v="170"/>
+    <s v="null"/>
+    <n v="34"/>
+    <n v="14.11"/>
+    <n v="11.39"/>
+    <n v="5.0999999999999996"/>
+    <n v="30.6"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="22"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Mezcla fisica 1"/>
+    <n v="238"/>
+    <s v="null"/>
+    <n v="47.6"/>
+    <n v="2.38"/>
+    <n v="26.18"/>
+    <n v="7.14"/>
+    <n v="42.84"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Mezcla fisica 2"/>
+    <n v="204"/>
+    <s v="null"/>
+    <n v="24.48"/>
+    <n v="2.04"/>
+    <n v="22.44"/>
+    <n v="8.16"/>
+    <n v="55.08"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="20"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Mezcla fisica 2"/>
+    <n v="238"/>
+    <s v="null"/>
+    <n v="28.56"/>
+    <n v="2.38"/>
+    <n v="26.18"/>
+    <n v="9.52"/>
+    <n v="64.260000000000005"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="21"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Mezcla fisica 3"/>
+    <n v="170"/>
+    <s v="null"/>
+    <n v="34"/>
+    <n v="14.11"/>
+    <n v="11.39"/>
+    <n v="5.0999999999999996"/>
+    <n v="30.6"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9EA4DB62-CF08-4DFE-BF3B-6CB7FDF9BF73}" name="PivotTable2" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="6">
+  <location ref="A5:G12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
+  <pivotFields count="13">
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="25">
+        <item x="13"/>
+        <item x="22"/>
+        <item x="19"/>
+        <item x="14"/>
+        <item x="18"/>
+        <item x="23"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="20"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="17"/>
+        <item x="21"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="12"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="3"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="3">
+    <pageField fld="0" hier="-1"/>
+    <pageField fld="2" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Average of Cantidad_Kg_ha" fld="6" subtotal="average" baseField="1" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -619,17 +4870,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA3D38B-9E40-4E9F-8415-A4349BC7491D}">
   <dimension ref="A1:M149"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -670,7 +4921,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -711,36 +4962,36 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G3" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I3" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
         <v>5.5</v>
@@ -752,7 +5003,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>32</v>
       </c>
@@ -793,36 +5044,36 @@
         <v>9.99</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G5" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J5" s="1">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K5" s="1">
         <v>0</v>
@@ -834,7 +5085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
@@ -875,7 +5126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -916,7 +5167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -957,33 +5208,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="1">
         <v>50</v>
       </c>
-      <c r="G9" s="1">
-        <v>58.7</v>
-      </c>
       <c r="H9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I9" s="1">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -998,36 +5249,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="1">
         <v>50</v>
       </c>
-      <c r="G10" s="1">
-        <v>58.6</v>
-      </c>
       <c r="H10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I10" s="1">
-        <v>26.96</v>
+        <v>10.5</v>
       </c>
       <c r="J10" s="1">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="K10" s="1">
         <v>26.96</v>
@@ -1039,7 +5290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
@@ -1080,7 +5331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
@@ -1121,7 +5372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>32</v>
       </c>
@@ -1162,33 +5413,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G14" s="1">
-        <v>50</v>
+        <v>58.7</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I14" s="1">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J14" s="1">
         <v>0</v>
@@ -1203,7 +5454,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1244,7 +5495,7 @@
         <v>24.96</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>32</v>
       </c>
@@ -1285,7 +5536,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -1326,36 +5577,36 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G18" s="1">
-        <v>50</v>
+        <v>58.6</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I18" s="1">
-        <v>10.5</v>
+        <v>26.96</v>
       </c>
       <c r="J18" s="1">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -1367,7 +5618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
@@ -1408,7 +5659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>32</v>
       </c>
@@ -1449,7 +5700,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>32</v>
       </c>
@@ -1490,7 +5741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
@@ -1531,7 +5782,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
@@ -1572,7 +5823,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
@@ -1613,7 +5864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
@@ -1654,7 +5905,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
@@ -1695,7 +5946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
@@ -1736,7 +5987,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -1777,7 +6028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>34</v>
       </c>
@@ -1818,7 +6069,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>34</v>
       </c>
@@ -1859,7 +6110,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -1900,7 +6151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>34</v>
       </c>
@@ -1941,7 +6192,7 @@
         <v>24.96</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>34</v>
       </c>
@@ -1982,7 +6233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>11</v>
       </c>
@@ -2023,7 +6274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>11</v>
       </c>
@@ -2064,7 +6315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>11</v>
       </c>
@@ -2105,7 +6356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>11</v>
       </c>
@@ -2146,7 +6397,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>11</v>
       </c>
@@ -2187,7 +6438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>11</v>
       </c>
@@ -2228,7 +6479,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>11</v>
       </c>
@@ -2269,7 +6520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>11</v>
       </c>
@@ -2310,7 +6561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>11</v>
       </c>
@@ -2351,7 +6602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>11</v>
       </c>
@@ -2392,7 +6643,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>11</v>
       </c>
@@ -2433,7 +6684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>32</v>
       </c>
@@ -2474,7 +6725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>32</v>
       </c>
@@ -2515,7 +6766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>32</v>
       </c>
@@ -2556,7 +6807,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>32</v>
       </c>
@@ -2597,7 +6848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>32</v>
       </c>
@@ -2638,7 +6889,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>32</v>
       </c>
@@ -2679,7 +6930,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>32</v>
       </c>
@@ -2720,7 +6971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>32</v>
       </c>
@@ -2761,7 +7012,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,7 +7053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>32</v>
       </c>
@@ -2843,7 +7094,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>34</v>
       </c>
@@ -2884,7 +7135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>34</v>
       </c>
@@ -2925,7 +7176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>34</v>
       </c>
@@ -2966,7 +7217,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>34</v>
       </c>
@@ -3007,7 +7258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>34</v>
       </c>
@@ -3048,7 +7299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>34</v>
       </c>
@@ -3089,7 +7340,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>34</v>
       </c>
@@ -3130,7 +7381,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>34</v>
       </c>
@@ -3171,7 +7422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>34</v>
       </c>
@@ -3212,7 +7463,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>34</v>
       </c>
@@ -3253,11 +7504,11 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="1">
         <v>59</v>
       </c>
       <c r="C65" s="1" t="s">
@@ -3294,7 +7545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>34</v>
       </c>
@@ -3335,7 +7586,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>34</v>
       </c>
@@ -3376,7 +7627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>34</v>
       </c>
@@ -3417,7 +7668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>34</v>
       </c>
@@ -3458,7 +7709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>34</v>
       </c>
@@ -3499,7 +7750,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>34</v>
       </c>
@@ -3540,7 +7791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>34</v>
       </c>
@@ -3581,7 +7832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>34</v>
       </c>
@@ -3622,7 +7873,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>34</v>
       </c>
@@ -3663,7 +7914,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>34</v>
       </c>
@@ -3704,7 +7955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>34</v>
       </c>
@@ -3745,7 +7996,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>34</v>
       </c>
@@ -3786,7 +8037,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>34</v>
       </c>
@@ -3827,7 +8078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>34</v>
       </c>
@@ -3868,7 +8119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>34</v>
       </c>
@@ -3909,7 +8160,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>34</v>
       </c>
@@ -3950,7 +8201,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>34</v>
       </c>
@@ -3991,7 +8242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>34</v>
       </c>
@@ -4032,7 +8283,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>11</v>
       </c>
@@ -4073,7 +8324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>11</v>
       </c>
@@ -4114,7 +8365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>11</v>
       </c>
@@ -4155,7 +8406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>11</v>
       </c>
@@ -4196,7 +8447,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>11</v>
       </c>
@@ -4237,7 +8488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>11</v>
       </c>
@@ -4278,7 +8529,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>11</v>
       </c>
@@ -4319,7 +8570,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>11</v>
       </c>
@@ -4360,7 +8611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>11</v>
       </c>
@@ -4401,7 +8652,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>11</v>
       </c>
@@ -4442,7 +8693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>11</v>
       </c>
@@ -4483,7 +8734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>11</v>
       </c>
@@ -4524,7 +8775,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>11</v>
       </c>
@@ -4565,7 +8816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>11</v>
       </c>
@@ -4606,7 +8857,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>11</v>
       </c>
@@ -4647,7 +8898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>32</v>
       </c>
@@ -4688,7 +8939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>32</v>
       </c>
@@ -4729,7 +8980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>32</v>
       </c>
@@ -4770,7 +9021,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>32</v>
       </c>
@@ -4811,7 +9062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>32</v>
       </c>
@@ -4852,7 +9103,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>32</v>
       </c>
@@ -4893,7 +9144,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>32</v>
       </c>
@@ -4934,7 +9185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>32</v>
       </c>
@@ -4975,7 +9226,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>32</v>
       </c>
@@ -5016,7 +9267,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>32</v>
       </c>
@@ -5057,7 +9308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>32</v>
       </c>
@@ -5098,7 +9349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>32</v>
       </c>
@@ -5139,7 +9390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>32</v>
       </c>
@@ -5180,7 +9431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>32</v>
       </c>
@@ -5221,7 +9472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>32</v>
       </c>
@@ -5262,7 +9513,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>11</v>
       </c>
@@ -5303,7 +9554,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>11</v>
       </c>
@@ -5344,7 +9595,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>11</v>
       </c>
@@ -5385,7 +9636,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>11</v>
       </c>
@@ -5426,7 +9677,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>32</v>
       </c>
@@ -5467,7 +9718,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>32</v>
       </c>
@@ -5508,7 +9759,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>32</v>
       </c>
@@ -5549,7 +9800,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>32</v>
       </c>
@@ -5590,7 +9841,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>34</v>
       </c>
@@ -5631,7 +9882,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>34</v>
       </c>
@@ -5672,7 +9923,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>34</v>
       </c>
@@ -5713,7 +9964,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>34</v>
       </c>
@@ -5754,7 +10005,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>11</v>
       </c>
@@ -5795,7 +10046,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>11</v>
       </c>
@@ -5836,7 +10087,7 @@
         <v>45.9</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>11</v>
       </c>
@@ -5877,7 +10128,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>11</v>
       </c>
@@ -5918,7 +10169,7 @@
         <v>24.48</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>32</v>
       </c>
@@ -5959,7 +10210,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>32</v>
       </c>
@@ -6000,7 +10251,7 @@
         <v>45.9</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>32</v>
       </c>
@@ -6041,7 +10292,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>32</v>
       </c>
@@ -6082,7 +10333,7 @@
         <v>24.48</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>34</v>
       </c>
@@ -6123,7 +10374,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>34</v>
       </c>
@@ -6164,7 +10415,7 @@
         <v>45.9</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>34</v>
       </c>
@@ -6205,7 +10456,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>34</v>
       </c>
@@ -6246,7 +10497,7 @@
         <v>24.48</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>11</v>
       </c>
@@ -6287,7 +10538,7 @@
         <v>42.84</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>11</v>
       </c>
@@ -6328,7 +10579,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>11</v>
       </c>
@@ -6369,7 +10620,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>11</v>
       </c>
@@ -6410,7 +10661,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>32</v>
       </c>
@@ -6451,7 +10702,7 @@
         <v>42.84</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>32</v>
       </c>
@@ -6492,7 +10743,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>32</v>
       </c>
@@ -6533,7 +10784,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>32</v>
       </c>
@@ -6574,7 +10825,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>34</v>
       </c>
@@ -6615,7 +10866,7 @@
         <v>42.84</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>34</v>
       </c>
@@ -6656,7 +10907,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>34</v>
       </c>
@@ -6697,7 +10948,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>34</v>
       </c>
@@ -6739,7 +10990,181 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J149" xr:uid="{3CA3D38B-9E40-4E9F-8415-A4349BC7491D}"/>
+  <autoFilter ref="A1:J149" xr:uid="{3CA3D38B-9E40-4E9F-8415-A4349BC7491D}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J18">
+      <sortCondition ref="D1:D149"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AEDA409-4E84-4BE8-ABC7-F988066312C2}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="4">
+        <v>112.5</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4">
+        <v>64.099999999999994</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4">
+        <v>58.333333333333336</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4">
+        <v>58.333333333333336</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4">
+        <v>50.150000000000006</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4">
+        <v>50.150000000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4">
+        <v>58.6</v>
+      </c>
+      <c r="G11" s="4">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="4">
+        <v>112.5</v>
+      </c>
+      <c r="C12" s="4">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="D12" s="4">
+        <v>58.333333333333336</v>
+      </c>
+      <c r="E12" s="4">
+        <v>50.150000000000006</v>
+      </c>
+      <c r="F12" s="4">
+        <v>58.6</v>
+      </c>
+      <c r="G12" s="4">
+        <v>68.710000000000008</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>